--- a/03.舞台監督/精算.xlsx
+++ b/03.舞台監督/精算.xlsx
@@ -1,35 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aokib\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\青木智之\Desktop\aoki\files\2026.03 WAN-WAN BOTAN\03.舞台監督\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB7A56EC-652C-4AC1-B0B9-1AD8C8C00EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4DD40C-BC48-482F-8DEE-6BF36D976DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="全て" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="レシート合計" sheetId="3" r:id="rId1"/>
+    <sheet name="全て" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">全て!$B$2:$H$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">レシート合計!$B$4:$D$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">全て!$B$4:$H$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="57">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -389,7 +401,87 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>AJ606 S2.0 カーテンレール</t>
+    <t>合計</t>
+    <rPh sb="0" eb="2">
+      <t>ゴウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⇒税額算出方法が店舗ごとに異なるため、上記金額は実際のレシート合計と相違します。
+上記金額は誤りです。</t>
+    <rPh sb="1" eb="3">
+      <t>ゼイガク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サンシュツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テンポ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジョウキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ソウイ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ジョウキ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>アヤマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⇒レシート金額は全て税込み価格で記載しています。</t>
+    <rPh sb="5" eb="7">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ゼイコ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カカク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レシート金額合計</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>購入明細</t>
+    <rPh sb="0" eb="2">
+      <t>コウニュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>メイサイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -397,7 +489,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -410,6 +502,20 @@
       <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -454,7 +560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -462,6 +568,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -741,8 +854,223 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{639A35B5-F748-4862-AC9A-2A87F2500770}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:D21"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="3.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.3984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" ht="35.4">
+      <c r="B2" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="28.8">
+      <c r="B3" s="8"/>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="B4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="B5" s="3">
+        <v>46081</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1466</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2466</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="B7" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2980</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C8" s="2">
+        <v>30797</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="B9" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C9" s="2">
+        <v>220</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10" s="3">
+        <v>46089</v>
+      </c>
+      <c r="C10" s="2">
+        <v>11522</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="B11" s="3">
+        <v>46090</v>
+      </c>
+      <c r="C11" s="2">
+        <v>26520</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="B12" s="3">
+        <v>46095</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2069</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="B13" s="3">
+        <v>46096</v>
+      </c>
+      <c r="C13" s="2">
+        <v>9948</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="B14" s="3">
+        <v>46101</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1155</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="B15" s="3">
+        <v>46101</v>
+      </c>
+      <c r="C15" s="2">
+        <v>13880</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="B16" s="3">
+        <v>46102</v>
+      </c>
+      <c r="C16" s="6">
+        <v>22000</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" s="3">
+        <v>46102</v>
+      </c>
+      <c r="C17" s="2">
+        <v>5706</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18" s="3">
+        <v>46103</v>
+      </c>
+      <c r="C18" s="2">
+        <v>2578</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="C20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="5">
+        <f>SUM(C5:C18)</f>
+        <v>133307</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="D21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B4:D4" xr:uid="{639A35B5-F748-4862-AC9A-2A87F2500770}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:D18">
+      <sortCondition ref="B4"/>
+    </sortState>
+  </autoFilter>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:H50"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:H53"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="3.69921875" customWidth="1"/>
@@ -751,127 +1079,82 @@
     <col min="7" max="7" width="14.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8">
-      <c r="B2" s="4" t="s">
+    <row r="2" spans="2:8" ht="35.4">
+      <c r="B2" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8">
-      <c r="B3" s="3">
-        <v>46102</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="2">
-        <v>2728</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2">
-        <f>D3*E3</f>
-        <v>2728</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="2">
-        <f>F3</f>
-        <v>2728</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8">
-      <c r="B4" s="3">
-        <v>46102</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="2">
-        <v>2728</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2">
-        <f t="shared" ref="F4:F48" si="0">D4*E4</f>
-        <v>2728</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="2">
-        <f t="shared" ref="H4:H48" si="1">F4</f>
-        <v>2728</v>
       </c>
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="3">
-        <v>46102</v>
+        <v>46081</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2">
-        <v>22000</v>
+        <v>745</v>
       </c>
       <c r="E5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <f t="shared" si="0"/>
-        <v>22000</v>
+        <f>D5*E5</f>
+        <v>1490</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H5" s="2">
-        <f t="shared" si="1"/>
-        <v>22000</v>
+        <f>F5</f>
+        <v>1490</v>
       </c>
     </row>
     <row r="6" spans="2:8">
       <c r="B6" s="3">
-        <v>46082</v>
+        <v>46081</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="D6" s="2">
-        <v>327</v>
+        <v>-44</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
       </c>
       <c r="F6" s="2">
-        <f t="shared" si="0"/>
-        <v>327</v>
+        <f>D6*E6</f>
+        <v>-44</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="H6" s="2">
-        <f t="shared" si="1"/>
-        <v>327</v>
+        <f>F6</f>
+        <v>-44</v>
       </c>
     </row>
     <row r="7" spans="2:8">
@@ -879,24 +1162,24 @@
         <v>46082</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" s="2">
-        <v>712</v>
+        <v>327</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
       </c>
       <c r="F7" s="2">
-        <f t="shared" si="0"/>
-        <v>712</v>
+        <f>D7*E7</f>
+        <v>327</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="H7" s="2">
-        <f t="shared" si="1"/>
-        <v>712</v>
+        <f>F7</f>
+        <v>327</v>
       </c>
     </row>
     <row r="8" spans="2:8">
@@ -904,7 +1187,7 @@
         <v>46082</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" s="2">
         <v>712</v>
@@ -913,14 +1196,14 @@
         <v>1</v>
       </c>
       <c r="F8" s="2">
-        <f t="shared" si="0"/>
+        <f>D8*E8</f>
         <v>712</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="H8" s="2">
-        <f t="shared" si="1"/>
+        <f>F8</f>
         <v>712</v>
       </c>
     </row>
@@ -929,7 +1212,7 @@
         <v>46082</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D9" s="2">
         <v>712</v>
@@ -938,65 +1221,65 @@
         <v>1</v>
       </c>
       <c r="F9" s="2">
-        <f t="shared" si="0"/>
+        <f>D9*E9</f>
         <v>712</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="H9" s="2">
-        <f t="shared" si="1"/>
+        <f>F9</f>
         <v>712</v>
       </c>
     </row>
     <row r="10" spans="2:8">
       <c r="B10" s="3">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D10" s="2">
-        <v>745</v>
+        <v>712</v>
       </c>
       <c r="E10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2">
-        <f t="shared" si="0"/>
-        <v>1490</v>
+        <f>D10*E10</f>
+        <v>712</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="H10" s="2">
-        <f t="shared" si="1"/>
-        <v>1490</v>
+        <f>F10</f>
+        <v>712</v>
       </c>
     </row>
     <row r="11" spans="2:8">
       <c r="B11" s="3">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D11" s="2">
-        <v>-44</v>
+        <v>2980</v>
       </c>
       <c r="E11" s="2">
         <v>1</v>
       </c>
       <c r="F11" s="2">
-        <f t="shared" ref="F11" si="2">D11*E11</f>
-        <v>-44</v>
+        <f>D11*E11</f>
+        <v>2980</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H11" s="2">
-        <f t="shared" si="1"/>
-        <v>-44</v>
+        <f>F11 * 1.1</f>
+        <v>3278.0000000000005</v>
       </c>
     </row>
     <row r="12" spans="2:8">
@@ -1004,24 +1287,24 @@
         <v>46082</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D12" s="2">
-        <v>2980</v>
+        <v>718</v>
       </c>
       <c r="E12" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F12" s="2">
-        <f t="shared" si="0"/>
-        <v>2980</v>
+        <f>D12*E12</f>
+        <v>9334</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H12" s="2">
         <f>F12 * 1.1</f>
-        <v>3278.0000000000005</v>
+        <v>10267.400000000001</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -1029,24 +1312,24 @@
         <v>46082</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D13" s="2">
-        <v>718</v>
+        <v>1580</v>
       </c>
       <c r="E13" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2">
-        <f t="shared" si="0"/>
-        <v>9334</v>
+        <f>D13*E13</f>
+        <v>1580</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H13" s="2">
         <f>F13 * 1.1</f>
-        <v>10267.400000000001</v>
+        <v>1738.0000000000002</v>
       </c>
     </row>
     <row r="14" spans="2:8">
@@ -1054,24 +1337,24 @@
         <v>46082</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="2">
-        <v>1580</v>
+        <v>198</v>
       </c>
       <c r="E14" s="2">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F14" s="2">
-        <f t="shared" si="0"/>
-        <v>1580</v>
+        <f>D14*E14</f>
+        <v>5940</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H14" s="2">
         <f>F14 * 1.1</f>
-        <v>1738.0000000000002</v>
+        <v>6534.0000000000009</v>
       </c>
     </row>
     <row r="15" spans="2:8">
@@ -1079,24 +1362,24 @@
         <v>46082</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D15" s="2">
-        <v>198</v>
+        <v>290</v>
       </c>
       <c r="E15" s="2">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F15" s="2">
-        <f t="shared" si="0"/>
-        <v>5940</v>
+        <f>D15*E15</f>
+        <v>5220</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H15" s="2">
         <f>F15 * 1.1</f>
-        <v>6534.0000000000009</v>
+        <v>5742.0000000000009</v>
       </c>
     </row>
     <row r="16" spans="2:8">
@@ -1104,24 +1387,24 @@
         <v>46082</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="D16" s="2">
-        <v>290</v>
+        <v>2680</v>
       </c>
       <c r="E16" s="2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2">
-        <f t="shared" si="0"/>
-        <v>5220</v>
+        <f>D16*E16</f>
+        <v>2680</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H16" s="2">
         <f>F16 * 1.1</f>
-        <v>5742.0000000000009</v>
+        <v>2948.0000000000005</v>
       </c>
     </row>
     <row r="17" spans="2:8">
@@ -1129,24 +1412,24 @@
         <v>46082</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="D17" s="2">
-        <v>2680</v>
+        <v>728</v>
       </c>
       <c r="E17" s="2">
         <v>1</v>
       </c>
       <c r="F17" s="2">
-        <f t="shared" si="0"/>
-        <v>2680</v>
+        <f>D17*E17</f>
+        <v>728</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H17" s="2">
         <f>F17 * 1.1</f>
-        <v>2948.0000000000005</v>
+        <v>800.80000000000007</v>
       </c>
     </row>
     <row r="18" spans="2:8">
@@ -1154,24 +1437,24 @@
         <v>46082</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D18" s="2">
-        <v>728</v>
+        <v>908</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
       </c>
       <c r="F18" s="2">
-        <f t="shared" si="0"/>
-        <v>728</v>
+        <f>D18*E18</f>
+        <v>908</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H18" s="2">
         <f>F18 * 1.1</f>
-        <v>800.80000000000007</v>
+        <v>998.80000000000007</v>
       </c>
     </row>
     <row r="19" spans="2:8">
@@ -1179,24 +1462,24 @@
         <v>46082</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D19" s="2">
-        <v>908</v>
+        <v>548</v>
       </c>
       <c r="E19" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19" s="2">
-        <f t="shared" si="0"/>
-        <v>908</v>
+        <f>D19*E19</f>
+        <v>1644</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H19" s="2">
         <f>F19 * 1.1</f>
-        <v>998.80000000000007</v>
+        <v>1808.4</v>
       </c>
     </row>
     <row r="20" spans="2:8">
@@ -1204,24 +1487,24 @@
         <v>46082</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D20" s="2">
-        <v>548</v>
+        <v>138</v>
       </c>
       <c r="E20" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" s="2">
-        <f t="shared" si="0"/>
-        <v>1644</v>
+        <f>D20*E20</f>
+        <v>276</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H20" s="2">
         <f>F20 * 1.1</f>
-        <v>1808.4</v>
+        <v>303.60000000000002</v>
       </c>
     </row>
     <row r="21" spans="2:8">
@@ -1229,24 +1512,24 @@
         <v>46082</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D21" s="2">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="E21" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" s="2">
-        <f t="shared" si="0"/>
-        <v>276</v>
+        <f>D21*E21</f>
+        <v>504</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H21" s="2">
         <f>F21 * 1.1</f>
-        <v>303.60000000000002</v>
+        <v>554.40000000000009</v>
       </c>
     </row>
     <row r="22" spans="2:8">
@@ -1254,24 +1537,24 @@
         <v>46082</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D22" s="2">
-        <v>168</v>
+        <v>-600</v>
       </c>
       <c r="E22" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2">
-        <f t="shared" si="0"/>
-        <v>504</v>
+        <f>D22*E22</f>
+        <v>-600</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H22" s="2">
-        <f>F22 * 1.1</f>
-        <v>554.40000000000009</v>
+        <f>F22</f>
+        <v>-600</v>
       </c>
     </row>
     <row r="23" spans="2:8">
@@ -1279,24 +1562,24 @@
         <v>46082</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23" s="2">
-        <v>-600</v>
+        <v>-216</v>
       </c>
       <c r="E23" s="2">
         <v>1</v>
       </c>
       <c r="F23" s="2">
-        <f t="shared" si="0"/>
-        <v>-600</v>
+        <f>D23*E23</f>
+        <v>-216</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H23" s="2">
-        <f t="shared" si="1"/>
-        <v>-600</v>
+        <f>F23</f>
+        <v>-216</v>
       </c>
     </row>
     <row r="24" spans="2:8">
@@ -1304,24 +1587,24 @@
         <v>46082</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D24" s="2">
-        <v>-216</v>
+        <v>200</v>
       </c>
       <c r="E24" s="2">
         <v>1</v>
       </c>
       <c r="F24" s="2">
-        <f t="shared" si="0"/>
-        <v>-216</v>
+        <f>D24*E24</f>
+        <v>200</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H24" s="2">
-        <f t="shared" si="1"/>
-        <v>-216</v>
+        <f>F24 * 1.1</f>
+        <v>220.00000000000003</v>
       </c>
     </row>
     <row r="25" spans="2:8">
@@ -1338,7 +1621,7 @@
         <v>20</v>
       </c>
       <c r="F25" s="2">
-        <f t="shared" si="0"/>
+        <f>D25*E25</f>
         <v>3960</v>
       </c>
       <c r="G25" s="2" t="s">
@@ -1363,7 +1646,7 @@
         <v>18</v>
       </c>
       <c r="F26" s="2">
-        <f t="shared" si="0"/>
+        <f>D26*E26</f>
         <v>5220</v>
       </c>
       <c r="G26" s="2" t="s">
@@ -1388,7 +1671,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="2">
-        <f t="shared" si="0"/>
+        <f>D27*E27</f>
         <v>-400</v>
       </c>
       <c r="G27" s="2" t="s">
@@ -1413,14 +1696,14 @@
         <v>1</v>
       </c>
       <c r="F28" s="2">
-        <f t="shared" si="0"/>
+        <f>D28*E28</f>
         <v>-216</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H28" s="2">
-        <f t="shared" si="1"/>
+        <f>F28</f>
         <v>-216</v>
       </c>
     </row>
@@ -1438,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="2">
-        <f t="shared" si="0"/>
+        <f>D29*E29</f>
         <v>297</v>
       </c>
       <c r="G29" s="2" t="s">
@@ -1463,7 +1746,7 @@
         <v>3</v>
       </c>
       <c r="F30" s="2">
-        <f t="shared" si="0"/>
+        <f>D30*E30</f>
         <v>1614</v>
       </c>
       <c r="G30" s="2" t="s">
@@ -1476,52 +1759,52 @@
     </row>
     <row r="31" spans="2:8">
       <c r="B31" s="3">
-        <v>46096</v>
+        <v>46090</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="D31" s="2">
-        <v>2508</v>
+        <v>170</v>
       </c>
       <c r="E31" s="2">
-        <v>1</v>
+        <v>156</v>
       </c>
       <c r="F31" s="2">
-        <f t="shared" si="0"/>
-        <v>2508</v>
+        <f>D31*E31</f>
+        <v>26520</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="H31" s="2">
-        <f t="shared" si="1"/>
-        <v>2508</v>
+        <f>F31</f>
+        <v>26520</v>
       </c>
     </row>
     <row r="32" spans="2:8">
       <c r="B32" s="3">
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D32" s="2">
-        <v>3058</v>
+        <v>2069</v>
       </c>
       <c r="E32" s="2">
         <v>1</v>
       </c>
       <c r="F32" s="2">
-        <f t="shared" si="0"/>
-        <v>3058</v>
+        <f>D32*E32</f>
+        <v>2069</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="H32" s="2">
-        <f t="shared" si="1"/>
-        <v>3058</v>
+        <f>F32</f>
+        <v>2069</v>
       </c>
     </row>
     <row r="33" spans="2:8">
@@ -1529,24 +1812,24 @@
         <v>46096</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="D33" s="2">
-        <v>822</v>
+        <v>2508</v>
       </c>
       <c r="E33" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33" s="2">
-        <f t="shared" si="0"/>
-        <v>2466</v>
+        <f>D33*E33</f>
+        <v>2508</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H33" s="2">
-        <f t="shared" si="1"/>
-        <v>2466</v>
+        <f>F33</f>
+        <v>2508</v>
       </c>
     </row>
     <row r="34" spans="2:8">
@@ -1554,24 +1837,24 @@
         <v>46096</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D34" s="2">
-        <v>767</v>
+        <v>3058</v>
       </c>
       <c r="E34" s="2">
         <v>1</v>
       </c>
       <c r="F34" s="2">
-        <f t="shared" si="0"/>
-        <v>767</v>
+        <f>D34*E34</f>
+        <v>3058</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H34" s="2">
-        <f t="shared" si="1"/>
-        <v>767</v>
+        <f>F34</f>
+        <v>3058</v>
       </c>
     </row>
     <row r="35" spans="2:8">
@@ -1579,24 +1862,24 @@
         <v>46096</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D35" s="2">
-        <v>602</v>
+        <v>822</v>
       </c>
       <c r="E35" s="2">
         <v>3</v>
       </c>
       <c r="F35" s="2">
-        <f t="shared" si="0"/>
-        <v>1806</v>
+        <f>D35*E35</f>
+        <v>2466</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H35" s="2">
-        <f t="shared" si="1"/>
-        <v>1806</v>
+        <f>F35</f>
+        <v>2466</v>
       </c>
     </row>
     <row r="36" spans="2:8">
@@ -1604,74 +1887,74 @@
         <v>46096</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D36" s="2">
-        <v>547</v>
+        <v>767</v>
       </c>
       <c r="E36" s="2">
         <v>1</v>
       </c>
       <c r="F36" s="2">
-        <f t="shared" si="0"/>
-        <v>547</v>
+        <f>D36*E36</f>
+        <v>767</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H36" s="2">
-        <f t="shared" si="1"/>
-        <v>547</v>
+        <f>F36</f>
+        <v>767</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" s="3">
-        <v>46101</v>
+        <v>46096</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D37" s="2">
-        <v>718</v>
+        <v>602</v>
       </c>
       <c r="E37" s="2">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F37" s="2">
-        <f t="shared" si="0"/>
-        <v>9334</v>
+        <f>D37*E37</f>
+        <v>1806</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H37" s="2">
-        <f>F37 * 1.1</f>
-        <v>10267.400000000001</v>
+        <f>F37</f>
+        <v>1806</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" s="3">
-        <v>46101</v>
+        <v>46096</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D38" s="2">
-        <v>297</v>
+        <v>547</v>
       </c>
       <c r="E38" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F38" s="2">
-        <f t="shared" si="0"/>
-        <v>891</v>
+        <f>D38*E38</f>
+        <v>547</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H38" s="2">
-        <f>F38 * 1.1</f>
-        <v>980.1</v>
+        <f>F38</f>
+        <v>547</v>
       </c>
     </row>
     <row r="39" spans="2:8">
@@ -1679,24 +1962,24 @@
         <v>46101</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D39" s="2">
-        <v>258</v>
+        <v>718</v>
       </c>
       <c r="E39" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F39" s="2">
-        <f t="shared" si="0"/>
-        <v>258</v>
+        <f>D39*E39</f>
+        <v>9334</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H39" s="2">
         <f>F39 * 1.1</f>
-        <v>283.8</v>
+        <v>10267.400000000001</v>
       </c>
     </row>
     <row r="40" spans="2:8">
@@ -1704,1187 +1987,298 @@
         <v>46101</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D40" s="2">
-        <v>178</v>
+        <v>297</v>
       </c>
       <c r="E40" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F40" s="2">
-        <f t="shared" si="0"/>
-        <v>2136</v>
+        <f>D40*E40</f>
+        <v>891</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H40" s="2">
         <f>F40 * 1.1</f>
-        <v>2349.6000000000004</v>
+        <v>980.1</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" s="3">
-        <v>46103</v>
+        <v>46101</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D41" s="2">
-        <v>448</v>
+        <v>258</v>
       </c>
       <c r="E41" s="2">
         <v>1</v>
       </c>
       <c r="F41" s="2">
-        <f t="shared" si="0"/>
-        <v>448</v>
+        <f>D41*E41</f>
+        <v>258</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H41" s="2">
         <f>F41 * 1.1</f>
-        <v>492.80000000000007</v>
+        <v>283.8</v>
       </c>
     </row>
     <row r="42" spans="2:8">
       <c r="B42" s="3">
-        <v>46103</v>
+        <v>46101</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D42" s="2">
-        <v>998</v>
+        <v>178</v>
       </c>
       <c r="E42" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F42" s="2">
-        <f t="shared" si="0"/>
-        <v>998</v>
+        <f>D42*E42</f>
+        <v>2136</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H42" s="2">
         <f>F42 * 1.1</f>
-        <v>1097.8000000000002</v>
+        <v>2349.6000000000004</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" s="3">
-        <v>46103</v>
+        <v>46101</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D43" s="2">
-        <v>848</v>
+        <v>1050</v>
       </c>
       <c r="E43" s="2">
         <v>1</v>
       </c>
       <c r="F43" s="2">
-        <f t="shared" si="0"/>
-        <v>848</v>
+        <f>D43*E43</f>
+        <v>1050</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H43" s="2">
         <f>F43 * 1.1</f>
-        <v>932.80000000000007</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" s="3">
-        <v>46103</v>
+        <v>46102</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="D44" s="2">
-        <v>50</v>
+        <v>2728</v>
       </c>
       <c r="E44" s="2">
         <v>1</v>
       </c>
       <c r="F44" s="2">
-        <f t="shared" si="0"/>
-        <v>50</v>
+        <f>D44*E44</f>
+        <v>2728</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H44" s="2">
-        <f>F44 * 1.1</f>
-        <v>55.000000000000007</v>
+        <f>F44</f>
+        <v>2728</v>
       </c>
     </row>
     <row r="45" spans="2:8">
       <c r="B45" s="3">
-        <v>46101</v>
+        <v>46102</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="D45" s="2">
-        <v>1050</v>
+        <v>2728</v>
       </c>
       <c r="E45" s="2">
         <v>1</v>
       </c>
       <c r="F45" s="2">
-        <f t="shared" si="0"/>
-        <v>1050</v>
+        <f>D45*E45</f>
+        <v>2728</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H45" s="2">
-        <f>F45 * 1.1</f>
-        <v>1155</v>
+        <f>F45</f>
+        <v>2728</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="3">
-        <v>46082</v>
+        <v>46102</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="D46" s="2">
-        <v>200</v>
+        <v>22000</v>
       </c>
       <c r="E46" s="2">
         <v>1</v>
       </c>
       <c r="F46" s="2">
-        <f t="shared" si="0"/>
-        <v>200</v>
+        <f>D46*E46</f>
+        <v>22000</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H46" s="2">
-        <f>F46 * 1.1</f>
-        <v>220.00000000000003</v>
+        <f>F46</f>
+        <v>22000</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" s="3">
-        <v>46095</v>
+        <v>46103</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D47" s="2">
-        <v>2069</v>
+        <v>448</v>
       </c>
       <c r="E47" s="2">
         <v>1</v>
       </c>
       <c r="F47" s="2">
-        <f t="shared" si="0"/>
-        <v>2069</v>
+        <f>D47*E47</f>
+        <v>448</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H47" s="2">
-        <f t="shared" si="1"/>
-        <v>2069</v>
+        <f>F47 * 1.1</f>
+        <v>492.80000000000007</v>
       </c>
     </row>
     <row r="48" spans="2:8">
       <c r="B48" s="3">
-        <v>46090</v>
+        <v>46103</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D48" s="2">
-        <v>170</v>
+        <v>998</v>
       </c>
       <c r="E48" s="2">
-        <v>156</v>
+        <v>1</v>
       </c>
       <c r="F48" s="2">
-        <f t="shared" si="0"/>
-        <v>26520</v>
+        <f>D48*E48</f>
+        <v>998</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="H48" s="2">
-        <f t="shared" si="1"/>
-        <v>26520</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3">
-      <c r="B50" t="s">
+        <f>F48 * 1.1</f>
+        <v>1097.8000000000002</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8">
+      <c r="B49" s="3">
+        <v>46103</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D49" s="2">
+        <v>848</v>
+      </c>
+      <c r="E49" s="2">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
+        <f>D49*E49</f>
+        <v>848</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H49" s="2">
+        <f>F49 * 1.1</f>
+        <v>932.80000000000007</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8">
+      <c r="B50" s="3">
+        <v>46103</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D50" s="2">
         <v>50</v>
       </c>
-      <c r="C50" s="1">
-        <f>SUM(H3:H48)</f>
-        <v>134681.80000000002</v>
+      <c r="E50" s="2">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <f>D50*E50</f>
+        <v>50</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H50" s="2">
+        <f>F50 * 1.1</f>
+        <v>55.000000000000007</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8">
+      <c r="B52" t="s">
+        <v>50</v>
+      </c>
+      <c r="C52" s="1">
+        <f>SUM(H5:H50)</f>
+        <v>134681.79999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" ht="54">
+      <c r="C53" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H48" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="B4:H50" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:H50">
+      <sortCondition ref="B4:B50"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA818873-25A9-48AA-8F77-DA0763DA8F7D}">
-  <dimension ref="B2:H40"/>
-  <sheetFormatPr defaultRowHeight="18"/>
-  <cols>
-    <col min="1" max="1" width="3.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.3984375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:8">
-      <c r="B2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8">
-      <c r="B3" s="3">
-        <v>46102</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="2">
-        <v>2728</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2">
-        <f>D3*E3</f>
-        <v>2728</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="2">
-        <f>F3</f>
-        <v>2728</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8">
-      <c r="B4" s="3">
-        <v>46102</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="2">
-        <v>2728</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2">
-        <f t="shared" ref="F4:F38" si="0">D4*E4</f>
-        <v>2728</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="2">
-        <f t="shared" ref="H4:H38" si="1">F4</f>
-        <v>2728</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8">
-      <c r="B5" s="3">
-        <v>46102</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="2">
-        <v>22000</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2">
-        <f t="shared" si="0"/>
-        <v>22000</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="2">
-        <f t="shared" si="1"/>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8">
-      <c r="B6" s="3">
-        <v>46082</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="2">
-        <v>327</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2">
-        <f t="shared" si="0"/>
-        <v>327</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="2">
-        <f t="shared" si="1"/>
-        <v>327</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8">
-      <c r="B7" s="3">
-        <v>46082</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="2">
-        <v>712</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2">
-        <f t="shared" si="0"/>
-        <v>712</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="2">
-        <f t="shared" si="1"/>
-        <v>712</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8">
-      <c r="B8" s="3">
-        <v>46082</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="2">
-        <v>712</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2">
-        <f t="shared" si="0"/>
-        <v>712</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="2">
-        <f t="shared" si="1"/>
-        <v>712</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8">
-      <c r="B9" s="3">
-        <v>46082</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="2">
-        <v>712</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2">
-        <f t="shared" si="0"/>
-        <v>712</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="2">
-        <f t="shared" si="1"/>
-        <v>712</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8">
-      <c r="B10" s="3">
-        <v>46081</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="2">
-        <v>745</v>
-      </c>
-      <c r="E10" s="2">
-        <v>2</v>
-      </c>
-      <c r="F10" s="2">
-        <f t="shared" si="0"/>
-        <v>1490</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="2">
-        <f t="shared" si="1"/>
-        <v>1490</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8">
-      <c r="B11" s="3">
-        <v>46081</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="2">
-        <v>-44</v>
-      </c>
-      <c r="E11" s="2">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2">
-        <f t="shared" si="0"/>
-        <v>-44</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="2">
-        <f t="shared" si="1"/>
-        <v>-44</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8">
-      <c r="B12" s="3">
-        <v>46082</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="2">
-        <v>2980</v>
-      </c>
-      <c r="E12" s="2">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2">
-        <f t="shared" si="0"/>
-        <v>2980</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="2">
-        <f>F12 * 1.1</f>
-        <v>3278.0000000000005</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8">
-      <c r="B13" s="3">
-        <v>46082</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="2">
-        <v>718</v>
-      </c>
-      <c r="E13" s="2">
-        <v>13</v>
-      </c>
-      <c r="F13" s="2">
-        <f t="shared" si="0"/>
-        <v>9334</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" s="2">
-        <f>F13 * 1.1</f>
-        <v>10267.400000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8">
-      <c r="B14" s="3">
-        <v>46082</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="2">
-        <v>1580</v>
-      </c>
-      <c r="E14" s="2">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2">
-        <f t="shared" si="0"/>
-        <v>1580</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="2">
-        <f>F14 * 1.1</f>
-        <v>1738.0000000000002</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8">
-      <c r="B15" s="3">
-        <v>46082</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="2">
-        <v>198</v>
-      </c>
-      <c r="E15" s="2">
-        <v>30</v>
-      </c>
-      <c r="F15" s="2">
-        <f t="shared" si="0"/>
-        <v>5940</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="2">
-        <f>F15 * 1.1</f>
-        <v>6534.0000000000009</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8">
-      <c r="B16" s="3">
-        <v>46082</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="2">
-        <v>290</v>
-      </c>
-      <c r="E16" s="2">
-        <v>18</v>
-      </c>
-      <c r="F16" s="2">
-        <f t="shared" si="0"/>
-        <v>5220</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16" s="2">
-        <f>F16 * 1.1</f>
-        <v>5742.0000000000009</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="3">
-        <v>46082</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="2">
-        <v>908</v>
-      </c>
-      <c r="E17" s="2">
-        <v>1</v>
-      </c>
-      <c r="F17" s="2">
-        <f t="shared" si="0"/>
-        <v>908</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17" s="2">
-        <f>F17 * 1.1</f>
-        <v>998.80000000000007</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="3">
-        <v>46082</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="2">
-        <v>-600</v>
-      </c>
-      <c r="E18" s="2">
-        <v>1</v>
-      </c>
-      <c r="F18" s="2">
-        <f t="shared" si="0"/>
-        <v>-600</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18" s="2">
-        <f t="shared" si="1"/>
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="3">
-        <v>46082</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="2">
-        <v>-216</v>
-      </c>
-      <c r="E19" s="2">
-        <v>1</v>
-      </c>
-      <c r="F19" s="2">
-        <f t="shared" si="0"/>
-        <v>-216</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H19" s="2">
-        <f t="shared" si="1"/>
-        <v>-216</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="3">
-        <v>46089</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="2">
-        <v>198</v>
-      </c>
-      <c r="E20" s="2">
-        <v>20</v>
-      </c>
-      <c r="F20" s="2">
-        <f t="shared" si="0"/>
-        <v>3960</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H20" s="2">
-        <f>F20 * 1.1</f>
-        <v>4356</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="3">
-        <v>46089</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="2">
-        <v>290</v>
-      </c>
-      <c r="E21" s="2">
-        <v>18</v>
-      </c>
-      <c r="F21" s="2">
-        <f t="shared" si="0"/>
-        <v>5220</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H21" s="2">
-        <f>F21 * 1.1</f>
-        <v>5742.0000000000009</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8">
-      <c r="B22" s="3">
-        <v>46089</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="2">
-        <v>-400</v>
-      </c>
-      <c r="E22" s="2">
-        <v>1</v>
-      </c>
-      <c r="F22" s="2">
-        <f t="shared" si="0"/>
-        <v>-400</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" s="2">
-        <f>F22</f>
-        <v>-400</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="3">
-        <v>46089</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="2">
-        <v>-216</v>
-      </c>
-      <c r="E23" s="2">
-        <v>1</v>
-      </c>
-      <c r="F23" s="2">
-        <f t="shared" si="0"/>
-        <v>-216</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H23" s="2">
-        <f t="shared" si="1"/>
-        <v>-216</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8">
-      <c r="B24" s="3">
-        <v>46089</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="2">
-        <v>297</v>
-      </c>
-      <c r="E24" s="2">
-        <v>1</v>
-      </c>
-      <c r="F24" s="2">
-        <f t="shared" si="0"/>
-        <v>297</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H24" s="2">
-        <f>F24 * 1.1</f>
-        <v>326.70000000000005</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8">
-      <c r="B25" s="3">
-        <v>46089</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="2">
-        <v>538</v>
-      </c>
-      <c r="E25" s="2">
-        <v>3</v>
-      </c>
-      <c r="F25" s="2">
-        <f t="shared" si="0"/>
-        <v>1614</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H25" s="2">
-        <f>F25 * 1.1</f>
-        <v>1775.4</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8">
-      <c r="B26" s="3">
-        <v>46096</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" s="2">
-        <v>2508</v>
-      </c>
-      <c r="E26" s="2">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2">
-        <f t="shared" si="0"/>
-        <v>2508</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H26" s="2">
-        <f t="shared" si="1"/>
-        <v>2508</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8">
-      <c r="B27" s="3">
-        <v>46096</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="2">
-        <v>3058</v>
-      </c>
-      <c r="E27" s="2">
-        <v>1</v>
-      </c>
-      <c r="F27" s="2">
-        <f t="shared" si="0"/>
-        <v>3058</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H27" s="2">
-        <f t="shared" si="1"/>
-        <v>3058</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8">
-      <c r="B28" s="3">
-        <v>46096</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" s="2">
-        <v>822</v>
-      </c>
-      <c r="E28" s="2">
-        <v>3</v>
-      </c>
-      <c r="F28" s="2">
-        <f t="shared" si="0"/>
-        <v>2466</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H28" s="2">
-        <f t="shared" si="1"/>
-        <v>2466</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8">
-      <c r="B29" s="3">
-        <v>46096</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" s="2">
-        <v>767</v>
-      </c>
-      <c r="E29" s="2">
-        <v>1</v>
-      </c>
-      <c r="F29" s="2">
-        <f t="shared" si="0"/>
-        <v>767</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H29" s="2">
-        <f t="shared" si="1"/>
-        <v>767</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8">
-      <c r="B30" s="3">
-        <v>46096</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30" s="2">
-        <v>602</v>
-      </c>
-      <c r="E30" s="2">
-        <v>3</v>
-      </c>
-      <c r="F30" s="2">
-        <f t="shared" si="0"/>
-        <v>1806</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H30" s="2">
-        <f t="shared" si="1"/>
-        <v>1806</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8">
-      <c r="B31" s="3">
-        <v>46096</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" s="2">
-        <v>547</v>
-      </c>
-      <c r="E31" s="2">
-        <v>1</v>
-      </c>
-      <c r="F31" s="2">
-        <f t="shared" si="0"/>
-        <v>547</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H31" s="2">
-        <f t="shared" si="1"/>
-        <v>547</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8">
-      <c r="B32" s="3">
-        <v>46101</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D32" s="2">
-        <v>297</v>
-      </c>
-      <c r="E32" s="2">
-        <v>3</v>
-      </c>
-      <c r="F32" s="2">
-        <f t="shared" si="0"/>
-        <v>891</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H32" s="2">
-        <f>F32 * 1.1</f>
-        <v>980.1</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8">
-      <c r="B33" s="3">
-        <v>46101</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="2">
-        <v>178</v>
-      </c>
-      <c r="E33" s="2">
-        <v>12</v>
-      </c>
-      <c r="F33" s="2">
-        <f t="shared" si="0"/>
-        <v>2136</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H33" s="2">
-        <f>F33 * 1.1</f>
-        <v>2349.6000000000004</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8">
-      <c r="B34" s="3">
-        <v>46103</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D34" s="2">
-        <v>448</v>
-      </c>
-      <c r="E34" s="2">
-        <v>1</v>
-      </c>
-      <c r="F34" s="2">
-        <f t="shared" si="0"/>
-        <v>448</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H34" s="2">
-        <f>F34 * 1.1</f>
-        <v>492.80000000000007</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8">
-      <c r="B35" s="3">
-        <v>46103</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D35" s="2">
-        <v>998</v>
-      </c>
-      <c r="E35" s="2">
-        <v>1</v>
-      </c>
-      <c r="F35" s="2">
-        <f t="shared" si="0"/>
-        <v>998</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="2">
-        <f>F35 * 1.1</f>
-        <v>1097.8000000000002</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8">
-      <c r="B36" s="3">
-        <v>46103</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D36" s="2">
-        <v>848</v>
-      </c>
-      <c r="E36" s="2">
-        <v>1</v>
-      </c>
-      <c r="F36" s="2">
-        <f t="shared" si="0"/>
-        <v>848</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H36" s="2">
-        <f>F36 * 1.1</f>
-        <v>932.80000000000007</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8">
-      <c r="B37" s="3">
-        <v>46095</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D37" s="2">
-        <v>2069</v>
-      </c>
-      <c r="E37" s="2">
-        <v>1</v>
-      </c>
-      <c r="F37" s="2">
-        <f t="shared" si="0"/>
-        <v>2069</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H37" s="2">
-        <f t="shared" si="1"/>
-        <v>2069</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8">
-      <c r="B38" s="3">
-        <v>46090</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D38" s="2">
-        <v>170</v>
-      </c>
-      <c r="E38" s="2">
-        <v>156</v>
-      </c>
-      <c r="F38" s="2">
-        <f t="shared" si="0"/>
-        <v>26520</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H38" s="2">
-        <f t="shared" si="1"/>
-        <v>26520</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8">
-      <c r="B40" t="s">
-        <v>50</v>
-      </c>
-      <c r="C40" s="1">
-        <f>SUM(H3:H38)</f>
-        <v>116285.40000000002</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="71" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>